--- a/downloads/forms/resignation.xlsx
+++ b/downloads/forms/resignation.xlsx
@@ -620,7 +620,7 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="6" t="n"/>
     </row>
-    <row r="8" ht="113.3858267716536" customHeight="1">
+    <row r="8" ht="226.7716535433071" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>세부 내용</t>
@@ -654,11 +654,11 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="62.36220472440945" customHeight="1"/>
+    <row r="15" ht="51.0236220472441" customHeight="1"/>
     <row r="16" ht="20.8" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">                              귀하</t>
+          <t>______________________________  귀하</t>
         </is>
       </c>
     </row>
